--- a/database/event/3373/event_3373_evp_summary.xlsx
+++ b/database/event/3373/event_3373_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5335</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5841</v>
+        <v>4.6821</v>
       </c>
       <c r="D2" t="n">
-        <v>3.026</v>
+        <v>3.0285</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5335</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9942</v>
+        <v>3.1767</v>
       </c>
       <c r="G2" t="n">
         <v>5.5393</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9942</v>
+        <v>3.1767</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4269</v>
+        <v>2.5748</v>
       </c>
       <c r="J2" t="n">
         <v>5.5393</v>
@@ -529,7 +529,7 @@
         <v>146</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9662</v>
+        <v>8.114100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>267</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7555</v>
+        <v>7.7647</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1662</v>
+        <v>4.1711</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7117</v>
+        <v>2.6495</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7555</v>
+        <v>7.7647</v>
       </c>
       <c r="F3" t="n">
-        <v>4.547</v>
+        <v>4.5562</v>
       </c>
       <c r="G3" t="n">
         <v>3.2085</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7332</v>
+        <v>5.7701</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6469</v>
+        <v>4.6769</v>
       </c>
       <c r="J3" t="n">
         <v>3.2085</v>
@@ -575,7 +575,7 @@
         <v>146</v>
       </c>
       <c r="M3" t="n">
-        <v>7.855399999999999</v>
+        <v>7.8854</v>
       </c>
       <c r="N3" t="n">
         <v>267</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9709</v>
+        <v>6.9875</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7447</v>
+        <v>3.7536</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3947</v>
+        <v>2.3399</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9709</v>
+        <v>6.9875</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8705</v>
+        <v>3.4301</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1004</v>
+        <v>3.5574</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8705</v>
+        <v>3.4301</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5161</v>
+        <v>3.4301</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1004</v>
+        <v>3.5574</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L4" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>6.616499999999999</v>
+        <v>6.9875</v>
       </c>
       <c r="N4" t="n">
-        <v>267</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5196</v>
+        <v>6.985</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5022</v>
+        <v>3.7522</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2124</v>
+        <v>2.3389</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5196</v>
+        <v>6.985</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7223</v>
+        <v>4.1877</v>
       </c>
       <c r="G5" t="n">
         <v>2.7973</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7223</v>
+        <v>4.2874</v>
       </c>
       <c r="I5" t="n">
-        <v>3.017</v>
+        <v>3.475</v>
       </c>
       <c r="J5" t="n">
         <v>2.7973</v>
@@ -667,7 +667,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>5.814299999999999</v>
+        <v>6.2723</v>
       </c>
       <c r="N5" t="n">
         <v>267</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0568</v>
+        <v>6.9709</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2536</v>
+        <v>3.7447</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0255</v>
+        <v>2.3333</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0568</v>
+        <v>6.9709</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4994</v>
+        <v>1.8705</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5574</v>
+        <v>5.1004</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4994</v>
+        <v>1.8705</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4994</v>
+        <v>1.5161</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5574</v>
+        <v>5.1004</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L6" t="n">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0568</v>
+        <v>6.616499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>216</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9453</v>
+        <v>4.9648</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6565</v>
+        <v>2.667</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5764</v>
+        <v>1.5341</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9453</v>
+        <v>4.9648</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4778</v>
+        <v>4.4973</v>
       </c>
       <c r="G7" t="n">
         <v>0.4675</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4549</v>
+        <v>5.533</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4213</v>
+        <v>4.4847</v>
       </c>
       <c r="J7" t="n">
         <v>0.4675</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8888</v>
+        <v>4.9522</v>
       </c>
       <c r="N7" t="n">
         <v>226</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3001</v>
+        <v>4.8652</v>
       </c>
       <c r="C8" t="n">
-        <v>2.31</v>
+        <v>2.6135</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3158</v>
+        <v>1.4944</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3001</v>
+        <v>4.8652</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5812</v>
+        <v>3.1463</v>
       </c>
       <c r="G8" t="n">
         <v>1.7189</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5812</v>
+        <v>3.1463</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0921</v>
+        <v>2.5502</v>
       </c>
       <c r="J8" t="n">
         <v>1.7189</v>
@@ -805,7 +805,7 @@
         <v>146</v>
       </c>
       <c r="M8" t="n">
-        <v>3.811</v>
+        <v>4.2691</v>
       </c>
       <c r="N8" t="n">
         <v>267</v>
@@ -814,403 +814,403 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9048</v>
+        <v>4.5546</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0976</v>
+        <v>2.4467</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1561</v>
+        <v>1.3706</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9048</v>
+        <v>4.5546</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9048</v>
+        <v>2.3504</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.2042</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9048</v>
+        <v>2.3504</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9413</v>
+        <v>2.3504</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.2042</v>
       </c>
       <c r="K9" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9413</v>
+        <v>4.554600000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>194</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7732</v>
+        <v>3.8757</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0269</v>
+        <v>2.082</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1029</v>
+        <v>1.1002</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7732</v>
+        <v>3.8757</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9527</v>
+        <v>3.8757</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1795</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9527</v>
+        <v>3.8757</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2038</v>
+        <v>3.9413</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1795</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0243</v>
+        <v>3.9413</v>
       </c>
       <c r="N10" t="n">
-        <v>226</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6987</v>
+        <v>3.8238</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9869</v>
+        <v>2.0541</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0728</v>
+        <v>1.0795</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6987</v>
+        <v>3.8238</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4801</v>
+        <v>4.0033</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2186</v>
+        <v>-0.1795</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4801</v>
+        <v>4.0033</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4801</v>
+        <v>3.2448</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2186</v>
+        <v>-0.1795</v>
       </c>
       <c r="K11" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6987</v>
+        <v>3.0653</v>
       </c>
       <c r="N11" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6566</v>
+        <v>3.6987</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9643</v>
+        <v>1.9869</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0558</v>
+        <v>1.0297</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6566</v>
+        <v>3.6987</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4524</v>
+        <v>2.4801</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2042</v>
+        <v>1.2186</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4524</v>
+        <v>2.4801</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4524</v>
+        <v>2.4801</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2042</v>
+        <v>1.2186</v>
       </c>
       <c r="K12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>223</v>
+        <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6566</v>
+        <v>3.6987</v>
       </c>
       <c r="N12" t="n">
-        <v>343</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.443</v>
+        <v>3.6059</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8495</v>
+        <v>1.937</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9695</v>
+        <v>0.9927</v>
       </c>
       <c r="E13" t="n">
-        <v>3.443</v>
+        <v>3.6059</v>
       </c>
       <c r="F13" t="n">
-        <v>3.443</v>
+        <v>4.1558</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.443</v>
+        <v>4.2132</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4752</v>
+        <v>4.2844</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4752</v>
+        <v>3.7345</v>
       </c>
       <c r="N13" t="n">
-        <v>194</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4331</v>
+        <v>3.5846</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8442</v>
+        <v>1.9256</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9655</v>
+        <v>0.9842</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4331</v>
+        <v>3.5846</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0462</v>
+        <v>2.3177</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3869</v>
+        <v>1.2669</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0462</v>
+        <v>2.3177</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0746</v>
+        <v>2.3177</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3869</v>
+        <v>1.2669</v>
       </c>
       <c r="K14" t="n">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="L14" t="n">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4615</v>
+        <v>3.5846</v>
       </c>
       <c r="N14" t="n">
-        <v>249</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.4167</v>
+        <v>3.4174</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8354</v>
+        <v>1.8358</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9589</v>
+        <v>0.9176</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4167</v>
+        <v>3.4174</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9666</v>
+        <v>3.4174</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5499000000000001</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9666</v>
+        <v>3.4174</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0036</v>
+        <v>3.4752</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5499000000000001</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4537</v>
+        <v>3.4752</v>
       </c>
       <c r="N15" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3856</v>
+        <v>3.4104</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8187</v>
+        <v>1.832</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9463</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3856</v>
+        <v>3.4104</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9837</v>
+        <v>3.0235</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4019</v>
+        <v>0.3869</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9837</v>
+        <v>3.0235</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9837</v>
+        <v>3.0746</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4019</v>
+        <v>0.3869</v>
       </c>
       <c r="K16" t="n">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="L16" t="n">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3856</v>
+        <v>3.4615</v>
       </c>
       <c r="N16" t="n">
-        <v>343</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.164</v>
+        <v>3.3856</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6997</v>
+        <v>1.8187</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8568</v>
+        <v>0.9049</v>
       </c>
       <c r="E17" t="n">
-        <v>3.164</v>
+        <v>3.3856</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8971</v>
+        <v>1.9837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2669</v>
+        <v>1.4019</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8971</v>
+        <v>1.9837</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8971</v>
+        <v>1.9837</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2669</v>
+        <v>1.4019</v>
       </c>
       <c r="K17" t="n">
         <v>120</v>
@@ -1219,7 +1219,7 @@
         <v>223</v>
       </c>
       <c r="M17" t="n">
-        <v>3.164</v>
+        <v>3.3856</v>
       </c>
       <c r="N17" t="n">
         <v>343</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0802</v>
+        <v>3.223</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6546</v>
+        <v>1.7314</v>
       </c>
       <c r="D18" t="n">
-        <v>0.823</v>
+        <v>0.8401</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0802</v>
+        <v>3.223</v>
       </c>
       <c r="F18" t="n">
-        <v>3.478</v>
+        <v>3.6208</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3978</v>
       </c>
       <c r="H18" t="n">
-        <v>3.478</v>
+        <v>3.6208</v>
       </c>
       <c r="I18" t="n">
-        <v>2.819</v>
+        <v>2.9347</v>
       </c>
       <c r="J18" t="n">
         <v>-0.3978</v>
@@ -1265,7 +1265,7 @@
         <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4212</v>
+        <v>2.5369</v>
       </c>
       <c r="N18" t="n">
         <v>226</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0791</v>
+        <v>3.1773</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6541</v>
+        <v>1.7068</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8225</v>
+        <v>0.8219</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0791</v>
+        <v>3.1773</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0791</v>
+        <v>3.1069</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0791</v>
+        <v>3.1069</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1078</v>
+        <v>3.1594</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="K19" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1078</v>
+        <v>3.2298</v>
       </c>
       <c r="N19" t="n">
-        <v>194</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9174</v>
+        <v>3.0562</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5672</v>
+        <v>1.6417</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7572</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9174</v>
+        <v>3.0562</v>
       </c>
       <c r="F20" t="n">
-        <v>2.847</v>
+        <v>3.0562</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.847</v>
+        <v>3.0562</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8735</v>
+        <v>3.1078</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9439</v>
+        <v>3.1078</v>
       </c>
       <c r="N20" t="n">
-        <v>269</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7191</v>
+        <v>2.8341</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4607</v>
+        <v>1.5224</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6771</v>
+        <v>0.6852</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7191</v>
+        <v>2.8341</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7191</v>
+        <v>2.8341</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7191</v>
+        <v>2.8341</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7317</v>
+        <v>2.858</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7317</v>
+        <v>2.858</v>
       </c>
       <c r="N21" t="n">
         <v>218</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1391</v>
+        <v>2.1758</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1491</v>
+        <v>1.1688</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4428</v>
+        <v>0.4229</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1391</v>
+        <v>2.1758</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1391</v>
+        <v>2.1758</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1391</v>
+        <v>2.1758</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1391</v>
+        <v>2.1941</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1391</v>
+        <v>2.1941</v>
       </c>
       <c r="N22" t="n">
-        <v>128</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0137</v>
+        <v>2.1391</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0817</v>
+        <v>1.1491</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3921</v>
+        <v>0.4083</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0137</v>
+        <v>2.1391</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8977</v>
+        <v>2.1391</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.884</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8977</v>
+        <v>2.1391</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9247</v>
+        <v>2.1391</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.884</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0407</v>
+        <v>2.1391</v>
       </c>
       <c r="N23" t="n">
-        <v>249</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9297</v>
+        <v>2.0477</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0366</v>
+        <v>1.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3582</v>
+        <v>0.3719</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9297</v>
+        <v>2.0477</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9297</v>
+        <v>2.0477</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9297</v>
+        <v>2.0477</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9387</v>
+        <v>2.0649</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9387</v>
+        <v>2.0649</v>
       </c>
       <c r="N24" t="n">
         <v>218</v>
@@ -1550,219 +1550,219 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8527</v>
+        <v>1.9921</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9952</v>
+        <v>1.0701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3271</v>
+        <v>0.3497</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8527</v>
+        <v>1.9921</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1951</v>
+        <v>2.8761</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3424</v>
+        <v>-0.884</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1951</v>
+        <v>2.8761</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2156</v>
+        <v>2.9247</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3424</v>
+        <v>-0.884</v>
       </c>
       <c r="K25" t="n">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8732</v>
+        <v>2.0407</v>
       </c>
       <c r="N25" t="n">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7105</v>
+        <v>1.8364</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9865</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2696</v>
+        <v>0.2877</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7105</v>
+        <v>1.8364</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7105</v>
+        <v>2.1788</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.3424</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7105</v>
+        <v>2.1788</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7105</v>
+        <v>2.2156</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.3424</v>
       </c>
       <c r="K26" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7105</v>
+        <v>1.8732</v>
       </c>
       <c r="N26" t="n">
-        <v>146</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4978</v>
+        <v>1.7148</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8046</v>
+        <v>0.9212</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1837</v>
+        <v>0.2393</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4978</v>
+        <v>1.7148</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4978</v>
+        <v>1.7148</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4978</v>
+        <v>1.7148</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4978</v>
+        <v>1.7293</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4978</v>
+        <v>1.7293</v>
       </c>
       <c r="N27" t="n">
-        <v>155</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4824</v>
+        <v>1.7105</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7963</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1775</v>
+        <v>0.2376</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4824</v>
+        <v>1.7105</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4824</v>
+        <v>1.7105</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4824</v>
+        <v>1.7105</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4893</v>
+        <v>1.7105</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4893</v>
+        <v>1.7105</v>
       </c>
       <c r="N28" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4249</v>
+        <v>1.575</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7654</v>
+        <v>0.8461</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1543</v>
+        <v>0.1836</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4249</v>
+        <v>1.575</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8404</v>
+        <v>1.1086</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5845</v>
+        <v>0.4664</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8404</v>
+        <v>1.1086</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8404</v>
+        <v>1.1086</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5845</v>
+        <v>0.4664</v>
       </c>
       <c r="K29" t="n">
         <v>120</v>
@@ -1771,7 +1771,7 @@
         <v>223</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4249</v>
+        <v>1.575</v>
       </c>
       <c r="N29" t="n">
         <v>343</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7309</v>
+        <v>0.8046</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1283</v>
+        <v>0.1528</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3607</v>
+        <v>1.4978</v>
       </c>
       <c r="N30" t="n">
         <v>155</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2639</v>
+        <v>1.4249</v>
       </c>
       <c r="C31" t="n">
-        <v>0.679</v>
+        <v>0.7654</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0892</v>
+        <v>0.1238</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2639</v>
+        <v>1.4249</v>
       </c>
       <c r="F31" t="n">
-        <v>2.238</v>
+        <v>0.8404</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9741</v>
+        <v>0.5845</v>
       </c>
       <c r="H31" t="n">
-        <v>2.238</v>
+        <v>0.8404</v>
       </c>
       <c r="I31" t="n">
-        <v>2.238</v>
+        <v>0.8404</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9741</v>
+        <v>0.5845</v>
       </c>
       <c r="K31" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2639</v>
+        <v>1.4249</v>
       </c>
       <c r="N31" t="n">
-        <v>216</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2458</v>
+        <v>1.4212</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6692</v>
+        <v>0.7634</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0819</v>
+        <v>0.1223</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2458</v>
+        <v>1.4212</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2458</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.3188</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2458</v>
+        <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2516</v>
+        <v>1.74</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.3188</v>
       </c>
       <c r="K32" t="n">
-        <v>218</v>
+        <v>125</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2516</v>
+        <v>1.4212</v>
       </c>
       <c r="N32" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2434</v>
+        <v>1.4048</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6679</v>
+        <v>0.7546</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0809</v>
+        <v>0.1158</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2434</v>
+        <v>1.4048</v>
       </c>
       <c r="F33" t="n">
-        <v>0.777</v>
+        <v>2.3789</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4664</v>
+        <v>-0.9741</v>
       </c>
       <c r="H33" t="n">
-        <v>0.777</v>
+        <v>2.3789</v>
       </c>
       <c r="I33" t="n">
-        <v>0.777</v>
+        <v>2.3789</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4664</v>
+        <v>-0.9741</v>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L33" t="n">
-        <v>223</v>
+        <v>91</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2434</v>
+        <v>1.4048</v>
       </c>
       <c r="N33" t="n">
-        <v>343</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1002</v>
+        <v>1.3607</v>
       </c>
       <c r="C34" t="n">
-        <v>0.591</v>
+        <v>0.7309</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0231</v>
+        <v>0.0982</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1002</v>
+        <v>1.3607</v>
       </c>
       <c r="F34" t="n">
-        <v>1.419</v>
+        <v>1.3607</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3188</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.419</v>
+        <v>1.3607</v>
       </c>
       <c r="I34" t="n">
-        <v>1.419</v>
+        <v>1.3607</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3188</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1002</v>
+        <v>1.3607</v>
       </c>
       <c r="N34" t="n">
-        <v>216</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>0.4953</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0489</v>
+        <v>-0.0765</v>
       </c>
       <c r="E35" t="n">
         <v>0.9221</v>
@@ -2066,7 +2066,7 @@
         <v>0.4845</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.057</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>0.9019</v>
@@ -2112,7 +2112,7 @@
         <v>0.4326</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.096</v>
+        <v>-0.1231</v>
       </c>
       <c r="E37" t="n">
         <v>0.8053</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6796</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3651</v>
+        <v>0.3593</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1468</v>
+        <v>-0.1774</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6796</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4396</v>
+        <v>1.4289</v>
       </c>
       <c r="G38" t="n">
         <v>-0.76</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4396</v>
+        <v>1.4289</v>
       </c>
       <c r="I38" t="n">
         <v>1.453</v>
@@ -2204,7 +2204,7 @@
         <v>0.1215</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.33</v>
+        <v>-0.3538</v>
       </c>
       <c r="E39" t="n">
         <v>0.2261</v>
@@ -2250,7 +2250,7 @@
         <v>0.11</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3387</v>
+        <v>-0.3624</v>
       </c>
       <c r="E40" t="n">
         <v>0.2047</v>
@@ -2296,7 +2296,7 @@
         <v>0.1096</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3389</v>
+        <v>-0.3626</v>
       </c>
       <c r="E41" t="n">
         <v>0.2041</v>
@@ -2342,7 +2342,7 @@
         <v>0.1057</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3419</v>
+        <v>-0.3655</v>
       </c>
       <c r="E42" t="n">
         <v>0.1968</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0887</v>
+        <v>0.0988</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3546</v>
+        <v>-0.3706</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1652</v>
+        <v>0.1839</v>
       </c>
       <c r="N43" t="n">
         <v>112</v>
@@ -2434,7 +2434,7 @@
         <v>0.073</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3665</v>
+        <v>-0.3898</v>
       </c>
       <c r="E44" t="n">
         <v>0.1359</v>
@@ -2480,7 +2480,7 @@
         <v>0.0449</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3876</v>
+        <v>-0.4106</v>
       </c>
       <c r="E45" t="n">
         <v>0.08359999999999999</v>
@@ -2516,127 +2516,127 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.09</v>
+        <v>0.0612</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0483</v>
+        <v>0.0329</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4577</v>
+        <v>-0.4195</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.09</v>
+        <v>0.0612</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.09</v>
+        <v>0.9663</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.9051</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.09</v>
+        <v>0.9663</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.09</v>
+        <v>0.9663</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.9051</v>
       </c>
       <c r="K46" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.09</v>
+        <v>0.06120000000000003</v>
       </c>
       <c r="N46" t="n">
-        <v>114</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1464</v>
+        <v>-0.09</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0786</v>
+        <v>-0.0483</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4805</v>
+        <v>-0.4798</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1464</v>
+        <v>-0.09</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.7502</v>
+        <v>-0.09</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6038</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7502</v>
+        <v>-0.09</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7572</v>
+        <v>-0.09</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6038</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>219</v>
+        <v>114</v>
       </c>
       <c r="L47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1534</v>
+        <v>-0.09</v>
       </c>
       <c r="N47" t="n">
-        <v>269</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1925</v>
+        <v>-0.1324</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1034</v>
+        <v>-0.0711</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4991</v>
+        <v>-0.4967</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1925</v>
+        <v>-0.1324</v>
       </c>
       <c r="F48" t="n">
-        <v>0.786</v>
+        <v>-0.7362</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.9785</v>
+        <v>0.6038</v>
       </c>
       <c r="H48" t="n">
-        <v>0.786</v>
+        <v>-0.7362</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7933</v>
+        <v>-0.7486</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9785</v>
+        <v>0.6038</v>
       </c>
       <c r="K48" t="n">
         <v>219</v>
@@ -2645,7 +2645,7 @@
         <v>50</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1852</v>
+        <v>-0.1448</v>
       </c>
       <c r="N48" t="n">
         <v>269</v>
@@ -2654,231 +2654,231 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2704</v>
+        <v>-0.1984</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1453</v>
+        <v>-0.1066</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5306</v>
+        <v>-0.523</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2704</v>
+        <v>-0.1984</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2704</v>
+        <v>0.7801</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.9785</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2704</v>
+        <v>0.7801</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2704</v>
+        <v>0.7933</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.9785</v>
       </c>
       <c r="K49" t="n">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2704</v>
+        <v>-0.1852</v>
       </c>
       <c r="N49" t="n">
-        <v>114</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DickStacy</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1607</v>
+        <v>-0.1175</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5422</v>
+        <v>-0.531</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2992</v>
+        <v>-0.2187</v>
       </c>
       <c r="N50" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>DickStacy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1655</v>
+        <v>-0.1607</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5458</v>
+        <v>-0.5631</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3081</v>
+        <v>-0.2992</v>
       </c>
       <c r="N51" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1868</v>
+        <v>-0.1655</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5619</v>
+        <v>-0.5667</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3478</v>
+        <v>-0.3081</v>
       </c>
       <c r="N52" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3798</v>
+        <v>-0.3478</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.204</v>
+        <v>-0.1868</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5748</v>
+        <v>-0.5825</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3798</v>
+        <v>-0.3478</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5253</v>
+        <v>-0.3478</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.9051</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5253</v>
+        <v>-0.3478</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5253</v>
+        <v>-0.3478</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.9051</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-0.3478</v>
+      </c>
+      <c r="N53" t="n">
         <v>91</v>
-      </c>
-      <c r="M53" t="n">
-        <v>-0.3798</v>
-      </c>
-      <c r="N53" t="n">
-        <v>216</v>
       </c>
     </row>
     <row r="54">
@@ -2894,7 +2894,7 @@
         <v>-0.2125</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.6015</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3955</v>
@@ -2930,185 +2930,185 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4002</v>
+        <v>-0.4009</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.215</v>
+        <v>-0.2154</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.583</v>
+        <v>-0.6036</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4002</v>
+        <v>-0.4009</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5998</v>
+        <v>-0.4009</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5998</v>
+        <v>-0.4009</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6054</v>
+        <v>-0.4077</v>
       </c>
       <c r="J55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3946</v>
+        <v>-0.4077</v>
       </c>
       <c r="N55" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4039</v>
+        <v>-0.4047</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.217</v>
+        <v>-0.2174</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5845</v>
+        <v>-0.6051</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4039</v>
+        <v>-0.4047</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4039</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4039</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4077</v>
+        <v>0.6054</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K56" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4077</v>
+        <v>-0.3946</v>
       </c>
       <c r="N56" t="n">
-        <v>194</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4227</v>
+        <v>-0.4212</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2271</v>
+        <v>-0.2263</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5921</v>
+        <v>-0.6117</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4227</v>
+        <v>-0.4212</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1165</v>
+        <v>-0.6834</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.5392</v>
+        <v>0.2622</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1165</v>
+        <v>-0.6834</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0944</v>
+        <v>-0.695</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.5392</v>
+        <v>0.2622</v>
       </c>
       <c r="K57" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="L57" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4448</v>
+        <v>-0.4328</v>
       </c>
       <c r="N57" t="n">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4264</v>
+        <v>-0.4227</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2291</v>
+        <v>-0.2271</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5936</v>
+        <v>-0.6123</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4264</v>
+        <v>-0.4227</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6886</v>
+        <v>0.1165</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2622</v>
+        <v>-0.5392</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6886</v>
+        <v>0.1165</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.695</v>
+        <v>0.0944</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2622</v>
+        <v>-0.5392</v>
       </c>
       <c r="K58" t="n">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="L58" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4328</v>
+        <v>-0.4448</v>
       </c>
       <c r="N58" t="n">
-        <v>249</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59">
@@ -3124,7 +3124,7 @@
         <v>-0.2342</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5975</v>
+        <v>-0.6176</v>
       </c>
       <c r="E59" t="n">
         <v>-0.436</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2782</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6502</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5178</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2805</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6323</v>
+        <v>-0.6519</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5221</v>
@@ -3252,400 +3252,400 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jnt</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.324</v>
+        <v>-0.3088</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.665</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6032</v>
+        <v>-0.5748</v>
       </c>
       <c r="N62" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HSK</t>
+          <t>jnt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3506</v>
+        <v>-0.324</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6842</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6526</v>
+        <v>-0.6032</v>
       </c>
       <c r="N63" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>HSK</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3752</v>
+        <v>-0.3506</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7035</v>
+        <v>-0.7039</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6984</v>
+        <v>-0.6526</v>
       </c>
       <c r="N64" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4192</v>
+        <v>-0.3752</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7366</v>
+        <v>-0.7222</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7804</v>
+        <v>-0.6984</v>
       </c>
       <c r="N65" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nak</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4614</v>
+        <v>-0.4192</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7684</v>
+        <v>-0.7548</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.859</v>
+        <v>-0.7804</v>
       </c>
       <c r="N66" t="n">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>nak</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4776</v>
+        <v>-0.4614</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7805</v>
+        <v>-0.7861</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.889</v>
+        <v>-0.859</v>
       </c>
       <c r="N67" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5664</v>
+        <v>-0.4776</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.7981</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0544</v>
+        <v>-0.889</v>
       </c>
       <c r="N68" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ngiN</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5954</v>
+        <v>-0.5664</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8691</v>
+        <v>-0.864</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1084</v>
+        <v>-1.0544</v>
       </c>
       <c r="N69" t="n">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>ngiN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.612</v>
+        <v>-0.5954</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.8855</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.1392</v>
+        <v>-1.1084</v>
       </c>
       <c r="N70" t="n">
         <v>114</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6344</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8984</v>
+        <v>-0.9144</v>
       </c>
       <c r="E71" t="n">
         <v>-1.1809</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6917</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9416</v>
+        <v>-0.9569</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2877</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6973</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9458</v>
+        <v>-0.9611</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2981</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3119</v>
+        <v>-1.3021</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7047</v>
+        <v>-0.6995</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9513</v>
+        <v>-0.9627</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3119</v>
+        <v>-1.3021</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3119</v>
+        <v>-1.3021</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3119</v>
+        <v>-1.3021</v>
       </c>
       <c r="I74" t="n">
         <v>-1.3241</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3392</v>
+        <v>-1.3342</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7194</v>
+        <v>-0.7167</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9624</v>
+        <v>-0.9755</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3392</v>
+        <v>-1.3342</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3392</v>
+        <v>-1.3342</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3392</v>
+        <v>-1.3342</v>
       </c>
       <c r="I75" t="n">
         <v>-1.3454</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7784</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0068</v>
+        <v>-1.0212</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4491</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7955</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0196</v>
+        <v>-1.0339</v>
       </c>
       <c r="E77" t="n">
         <v>-1.4809</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8047</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0265</v>
+        <v>-1.0407</v>
       </c>
       <c r="E78" t="n">
         <v>-1.4979</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8891</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.09</v>
+        <v>-1.1033</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6551</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8991</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0975</v>
+        <v>-1.1108</v>
       </c>
       <c r="E80" t="n">
         <v>-1.6738</v>
@@ -4136,7 +4136,7 @@
         <v>-0.9929</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.1681</v>
+        <v>-1.1803</v>
       </c>
       <c r="E81" t="n">
         <v>-1.8484</v>
